--- a/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.026Z</v>
+        <v>2026-07-14T13:50:03.712Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
@@ -428,7 +428,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.712Z</v>
+        <v>2026-07-17T19:29:57.602Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/04-gcb/parsed-excel/gcb republic house corporate(1061130000070)-sept.2023 - parsed.xlsx
@@ -32,11 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="4">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="m/d/yyyy&quot;  &quot;h\:mm\:ss\ AM/PM"/>
-    <numFmt numFmtId="165" formatCode="0;0"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -428,7 +425,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-17T19:29:57.602Z</v>
+        <v>2026-08-10T12:09:43.477Z</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +441,7 @@
         <v>Sum debits / payments</v>
       </c>
       <c r="B6">
-        <v>5191022.260000001</v>
+        <v>5199022.260000001</v>
       </c>
     </row>
     <row r="7">
@@ -4870,6 +4867,9 @@
       </c>
       <c r="D229" t="str">
         <v>22-Sep-2023</v>
+      </c>
+      <c r="E229">
+        <v>8000</v>
       </c>
       <c r="G229">
         <v>12321.1</v>
